--- a/Flormar-Teknik-SEO-Audit-12082026.xlsx
+++ b/Flormar-Teknik-SEO-Audit-12082026.xlsx
@@ -18,8 +18,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yonlendirmeler" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kaybedilen 1inci Sira" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="405 ve 404 Yanitlari" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structured Data" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yontem" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta Description Eksik" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structured Data" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yontem" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -623,20 +624,20 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Internal pages</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>5XX page</t>
+          <t>Multiple title tags / title outside &lt;head&gt;</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>5XX Sayfalar</t>
+          <t>Multiple Title</t>
         </is>
       </c>
     </row>
@@ -648,20 +649,20 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Internal pages</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Multiple title tags</t>
+          <t>5XX page (3 Ağu Ahrefs)</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Multiple Title</t>
+          <t>5XX Sayfalar</t>
         </is>
       </c>
     </row>
@@ -723,20 +724,20 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Rankings</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Mayıs'ta 1. sırada olup bugün olmayan kelime</t>
+          <t>H1 tag missing or empty</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Kaybedilen 1inci Sira</t>
+          <t>H1 Bulunmayan</t>
         </is>
       </c>
     </row>
@@ -748,20 +749,20 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Rankings</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>H1 tag missing or empty</t>
+          <t>Mayıs'ta 1. sırada olup bugün olmayan kelime</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>H1 Bulunmayan</t>
+          <t>Kaybedilen 1inci Sira</t>
         </is>
       </c>
     </row>
@@ -782,7 +783,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -793,25 +794,25 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Notice</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Internal pages</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Tarama sırasında 405 yanıtı (hız sınırı)</t>
+          <t>Meta description tag missing or empty</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>292</v>
+        <v>17</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>405 ve 404 Yanitlari</t>
+          <t>Meta Description Eksik</t>
         </is>
       </c>
     </row>
@@ -823,25 +824,50 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
+          <t>Internal pages</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Tarama sırasında 405 yanıtı (hız sınırı) ve 1 adet 404</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>338</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>405 ve 404 Yanitlari</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Notice</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Multiple H1 tags</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="D15" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Multiple H1</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>NOT: Önem dereceleri Ahrefs Site Audit sınıflandırmasından alınmıştır. Etkilenen URL sayısı, ilgili sheet'teki listeden fazla olabilir; sheet'ler trafiğe veya hacme göre sıralanmış öncelikli kesiti içerir.</t>
         </is>
@@ -1672,11 +1698,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:C341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="92" customWidth="1" min="1" max="1"/>
+    <col width="86" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1690,6 +1717,11 @@
           <t>Status Code</t>
         </is>
       </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Sayfa tipi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -1700,601 +1732,5071 @@
       <c r="B2" s="3" t="n">
         <v>404</v>
       </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Alt kırılım</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/mediterranean-yuksek-pigmentli-parlak-bitisli-oje-yesil-8682536113250/</t>
+          <t>https://www.flormar.com.tr/1-alana-1-hediye/?page=2</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/glam-kiss-yuksek-pigmentli-nemlendirici-cam-dudak-gorunumlu-parlak-bitisli-ruj-pembe-8682536113915/</t>
+          <t>https://www.flormar.com.tr/ISO-14001/</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/perfect-coverage-mavi-isik-korumali-hafif-yapili-likit-kapatici-pembe-8682536096416/</t>
+          <t>https://www.flormar.com.tr/ISO-22716/</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/vintage-romance-nail-enamel/</t>
+          <t>https://www.flormar.com.tr/ISO-45001/</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/k-spirit-collection/</t>
+          <t>https://www.flormar.com.tr/ISO-9001/</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/golden-glam-shimmer-oil-monoi-tahiti-ozlu-isiltili-sac-ve-vucut-yagi-transparan-8682536114066/</t>
+          <t>https://www.flormar.com.tr/akrep-burcu-3-lu-makyaj-seti-renkli-set112/</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/stay-perfect-concealer-corrector/</t>
+          <t>https://www.flormar.com.tr/allik/?page=3</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/latte-nail-enamel-yuksek-pigmentli-parlak-bitisli-oje-pembe-ten-rengi-8682536104517/</t>
+          <t>https://www.flormar.com.tr/aslan-burcu-3-lu-makyaj-seti-renkli-set106/</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/jelly-look-yuksek-pigmentli-parlak-bitisli-jel-gorunumlu-oje-mor-8690604497805/</t>
+          <t>https://www.flormar.com.tr/baked-yuksek-pigmentli-mat-bitisli-firinlanmis-goz-fari-turuncu-8682536052382/</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/color-joy-yuksek-pigmentli-parlak-bitisli-oje-turuncu-8682536078108/</t>
+          <t>https://www.flormar.com.tr/baked-yuksek-pigmentli-yogun-isiltili-firinlanmis-goz-fari-kahverengi-8682536052481/</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-transparan-8690604313266/</t>
+          <t>https://www.flormar.com.tr/baked-yuksek-pigmentli-yogun-isiltili-firinlanmis-goz-fari-pembe-8682536052405/</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/nail-enamel-yuksek-pigmentli-parlak-bitisli-oje-pembe-8682536054515/</t>
+          <t>https://www.flormar.com.tr/baked-yuksek-pigmentli-yogun-isiltili-firinlanmis-goz-fari-yesil-8682536052467/</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/jelly-look-4-lu-jel-gorunumlu-oje-seti-renkli-set019/</t>
+          <t>https://www.flormar.com.tr/baked-yuksek-pigmentli-yogun-isiltili-firinlanmis-goz-fari-yesil-8682536052504/</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/cheers-to-nails-3-lu-oje-seti-set142/</t>
+          <t>https://www.flormar.com.tr/balik-burcu-3-lu-makyaj-seti-pembe-set109/</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/beklemeyi-sevmeyenlere-hizli-kuruyan-5-li-oje-seti-renkli-set140/</t>
+          <t>https://www.flormar.com.tr/blossom-yogun-pigmentli-uzun-sure-kalici-parlak-bitisli-oje-turuncu-8682536091985/</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/kisa-hazir-tirnaklar-4-lu-tirnak-oje-seti-renkli-set124/</t>
+          <t>https://www.flormar.com.tr/blossom-yogun-pigmentli-uzun-sure-kalici-parlak-bitisli-oje-yesil-8682536092081/</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/sheer-up-sweet-escape-yari-transparan-parlak-bitisli-nemlendirici-ruj-kahverengi-8682536121392/</t>
+          <t>https://www.flormar.com.tr/blossom-yuksek-pigmentli-dogal-bitisli-uzun-sure-kalici-kremsi-allik-seftali-8682536091756/</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/yassi-kavisli-ic-bukey-uclu-kontur-fircasi-renksiz-8690604597741/</t>
+          <t>https://www.flormar.com.tr/blush-on-yuksek-pigmentli-mat-bitisli-kompakt-toz-allik-bronz-8682536083164/</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/puruzsuz-dokulu-3-lu-mini-makyaj-sungeri-seti-renksiz-8690604598588/</t>
+          <t>https://www.flormar.com.tr/blush-on-yuksek-pigmentli-mat-bitisli-kompakt-toz-allik-kirmizi-8682536083188/</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/asansor-kapakli-portatif-cok-amacli-kabuki-makyaj-fircasi-renksiz-8690604597680/</t>
+          <t>https://www.flormar.com.tr/blush-on-yuksek-pigmentli-mat-bitisli-kompakt-toz-allik-seftali-8682536083126/</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/silindir-yuvarlak-uclu-allik-fircasi-renksiz-8690604597697/</t>
+          <t>https://www.flormar.com.tr/boga-burcu-3-lu-makyaj-seti-renkli-set115/</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/arindirici-yumusatici-makyaj-fircasi-temizleme-jeli-renksiz-8690604629770/</t>
+          <t>https://www.flormar.com.tr/breathing-color-yuksek-pigmentli-parlak-bitisli-nefes-alan-oje-beyaz-8682536032537/</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/uzum-cekirdegi-yagi-iceren-guclu-etkili-oje-temizleyici-transparan-8682536034258/</t>
+          <t>https://www.flormar.com.tr/breathing-color-yuksek-pigmentli-parlak-bitisli-nefes-alan-oje-bordo-8682536032636/</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/omega-yagi-iceren-besleyici-oje-temizleyici-transparan-8682536034265/</t>
+          <t>https://www.flormar.com.tr/breathing-color-yuksek-pigmentli-parlak-bitisli-nefes-alan-oje-bordo-8682536054256/</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/e-vitamini-gliserin-iceren-asetonsuz-oje-temizleyici-transparan-8690604410361/</t>
+          <t>https://www.flormar.com.tr/breathing-color-yuksek-pigmentli-parlak-bitisli-nefes-alan-oje-kahverengi-8682536032612/</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/easy-go-kendinden-sungerli-pratik-oje-temizleyici-transparan-8682536034289/</t>
+          <t>https://www.flormar.com.tr/breathing-color-yuksek-pigmentli-parlak-bitisli-nefes-alan-oje-kirmizi-8682536054270/</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/badem-yagi-iceren-hizli-etkili-oje-temizleyici-transparan-8682536034272/</t>
+          <t>https://www.flormar.com.tr/breathing-color-yuksek-pigmentli-parlak-bitisli-nefes-alan-oje-lila-8682536032544/</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/skin-lifting-sikilastirici-bakim-yapan-kremsi-dokulu-spf-30-fondoten-pembe-8682536059718/</t>
+          <t>https://www.flormar.com.tr/breathing-color-yuksek-pigmentli-parlak-bitisli-nefes-alan-oje-mor-8682536054232/</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/k-spirit-cover-up-yuksek-kapatici-uzun-sure-kalici-dogal-bitisli-fondoten-bej-8682536114783/</t>
+          <t>https://www.flormar.com.tr/breathing-color-yuksek-pigmentli-parlak-bitisli-nefes-alan-oje-pembe-8682536032551/</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/k-spirit-cover-up-yuksek-kapatici-uzun-sure-kalici-yari-mat-bitisli-fondoten-kahverengi-8682536114851/</t>
+          <t>https://www.flormar.com.tr/breathing-color-yuksek-pigmentli-parlak-bitisli-nefes-alan-oje-pembe-8682536032582/</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/k-spirit-cover-up-yuksek-kapatici-uzun-sure-kalici-yari-mat-bitisli-fondoten-bej-8682536114493/</t>
+          <t>https://www.flormar.com.tr/breathing-color-yuksek-pigmentli-parlak-bitisli-nefes-alan-oje-pembe-8682536032599/</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/k-spirit-cover-up-yuksek-kapatici-uzun-sure-kalici-dogal-bitisli-fondoten-kahverengi-8682536114837/</t>
+          <t>https://www.flormar.com.tr/breathing-color-yuksek-pigmentli-parlak-bitisli-nefes-alan-oje-pembe-8682536032605/</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/k-spirit-cover-up-yuksek-kapatici-uzun-sure-kalici-yari-mat-bitisli-fondoten-kahverengi-8682536114868/</t>
+          <t>https://www.flormar.com.tr/breathing-color-yuksek-pigmentli-parlak-bitisli-nefes-alan-oje-pembe-8682536032629/</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/skin-lifting-sikilastirici-bakim-yapan-kremsi-dokulu-spf-30-fondoten-bej-8682536059558/</t>
+          <t>https://www.flormar.com.tr/breathing-color-yuksek-pigmentli-parlak-bitisli-nefes-alan-oje-pembe-8682536054171/</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/k-spirit-cover-up-yuksek-kapatici-uzun-sure-kalici-dogal-bitisli-fondoten-pembe-8682536114776/</t>
+          <t>https://www.flormar.com.tr/breathing-color-yuksek-pigmentli-parlak-bitisli-nefes-alan-oje-transparan-8682536032520/</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/k-spirit-cover-up-yuksek-kapatici-uzun-sure-kalici-yari-mat-bitisli-fondoten-bej-8682536114486/</t>
+          <t>https://www.flormar.com.tr/breathing-color-yuksek-pigmentli-parlak-bitisli-nefes-alan-oje-turkuaz-8682536054218/</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/skin-lifting-sikilastirici-bakim-yapan-kremsi-dokulu-spf-30-fondoten-pembe-8682536059534/</t>
+          <t>https://www.flormar.com.tr/breathing-color-yuksek-pigmentli-parlak-bitisli-nefes-alan-oje-turuncu-8682536032568/</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/k-spirit-cover-up-yuksek-kapatici-uzun-sure-kalici-yari-mat-bitisli-fondoten-bej-8682536114509/</t>
+          <t>https://www.flormar.com.tr/color-master-yuksek-pigmentli-mat-bitisli-ruj-pembe-8682536017985/</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/users/password/reset/</t>
+          <t>https://www.flormar.com.tr/color-palette-ince-yapili-mat-bitisli-isiltili-4-lu-goz-fari-paleti-beyaz-pembe-8682536121187/</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/tinted-moisturizer-esit-tonlu-isiltili-gorunum-veren-renkli-nemlendirici-ten-rengi-8682536041379/</t>
+          <t>https://www.flormar.com.tr/color-palette-ince-yapili-mat-bitisli-isiltili-4-lu-goz-fari-paleti-kahverengi-8682536107853/</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/gunes-koruyucu-bb-krem/</t>
+          <t>https://www.flormar.com.tr/color-palette-ince-yapili-mat-bitisli-isiltili-4-lu-goz-fari-paleti-pembe-8682536107877/</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/sun-lovers-nemlendirici-etkili-dogal-bitisli-renkli-gunes-koruyucu-spf50-bej-8682536090384/</t>
+          <t>https://www.flormar.com.tr/color-palette-ince-yapili-mat-bitisli-isiltili-4-lu-goz-fari-paleti-pembe-8682536121248/</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/tinted-moisturizer-esit-tonlu-isiltili-gorunum-veren-renkli-nemlendirici-pembe-8682536041393/</t>
+          <t>https://www.flormar.com.tr/color-palette-ince-yapili-mat-bitisli-isiltili-4-lu-goz-fari-paleti-sari-turuncu-altin-kahverengi-8682536107778/</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/tinted-moisturizer-esit-tonlu-isiltili-gorunum-veren-renkli-nemlendirici-pembe-8682536041362/</t>
+          <t>https://www.flormar.com.tr/color-palette-ince-yapili-mat-bitisli-isiltili-4-lu-goz-fari-paleti-sari-turuncu-altin-kahverengi-8682536121200/</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/sun-lovers-nemlendirici-etkili-dogal-bitisli-renkli-gunes-koruyucu-spf50-kahverengi-8682536090773/</t>
+          <t>https://www.flormar.com.tr/color-palette-ince-yapili-mat-bitisli-isiltili-4-lu-goz-fari-paleti-sari-turuncu-pembe-yesil-8682536107815/</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/sun-lovers-nemlendirici-etkili-dogal-bitisli-renkli-gunes-koruyucu-spf50-kahverengi-8682536090445/</t>
+          <t>https://www.flormar.com.tr/creamy-stylo-yuksek-pigmentli-yari-parlak-bitisli-kremsi-ruj-pembe-8682536108379/</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/sun-lovers-nemlendirici-etkili-dogal-bitisli-renkli-gunes-koruyucu-spf50-pembe-8682536090407/</t>
+          <t>https://www.flormar.com.tr/dewy-lip-booster-dolgunlastirici-etkili-seffaf-dogal-isiltili-dudak-parlaticisi-transparan-8690604619030/</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/sun-lovers-nemlendirici-etkili-dogal-bitisli-renkli-gunes-koruyucu-spf50-ten-rengi-8682536090360/</t>
+          <t>https://www.flormar.com.tr/dewy-lip-booster-dolgunlastirici-etkili-yari-transparan-dudak-parlaticisi-turuncu-8682536093927/</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/tinted-moisturizer-esit-tonlu-isiltili-gorunum-veren-renkli-nemlendirici-bej-8682536041409/</t>
+          <t>https://www.flormar.com.tr/dewy-lip-booster-dolgunlastirici-etkili-yari-transparan-dudak-parlaticisi-turuncu-8682536094023/</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/sun-lovers-nemlendirici-etkili-dogal-bitisli-renkli-gunes-koruyucu-spf50-pembe-8682536090346/</t>
+          <t>https://www.flormar.com.tr/dudak-kalemi/?page=3</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/love-basics-4lu-makyaj-seti-set274/</t>
+          <t>https://www.flormar.com.tr/dudak-parlaticisi/?page=3</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/shine-color-trio-3-lu-isiltili-goz-makyaj-seti-renkli-set276/</t>
+          <t>https://www.flormar.com.tr/dudak/?page=10</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/bordouex-lovers-makyaj-cantali-3-lu-makyaj-seti-set297/</t>
+          <t>https://www.flormar.com.tr/dudak/?page=11</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/makyaj-cantasi-ve-4-lu-makyaj-fircasi-seti-set298/</t>
+          <t>https://www.flormar.com.tr/dudak/?page=12</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/creamy-stylo-yuksek-pigmentli-yari-parlak-bitisli-kremsi-ruj-kahverengi-8682536013666/</t>
+          <t>https://www.flormar.com.tr/dudak/?page=3</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/creamy-stylo-yuksek-pigmentli-yari-parlak-bitisli-kremsi-ruj-pembe-8682536013727/</t>
+          <t>https://www.flormar.com.tr/dudak/?page=4</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/k-spirit-cover-up-yuksek-kapatici-uzun-sure-kalici-dogal-bitisli-fondoten-kahverengi-8682536114820/</t>
+          <t>https://www.flormar.com.tr/dudak/?page=5</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/k-spirit-cover-up-yuksek-kapatici-uzun-sure-kalici-dogal-bitisli-fondoten-bej-8682536114813/</t>
+          <t>https://www.flormar.com.tr/dudak/?page=6</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
         <v>405</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/k-spirit-cover-up-yuksek-kapatici-uzun-sure-kalici-yari-mat-bitisli-fondoten-bej-8682536114516/</t>
+          <t>https://www.flormar.com.tr/dudak/?page=7</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
         <v>405</v>
       </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/dudak/?page=8</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>NOT: A sütunundaki URL'ler 12 Ağu taramasında 405 yanıtı vermiştir. Ayrı bir kontrolde Googlebot, GPTBot, OAI-SearchBot, PerplexityBot ve ClaudeBot kullanıcı ajanlarının tamamı 200 yanıtı aldığından bu kayıtlar yoğun paralel taramaya karşı uygulanan hız sınırı olarak değerlendirilmiştir; sistematik bir erişim engeli tespit edilmemiştir. Liste toplam 292 kaydın ilk 60'ını kapsamaktadır.</t>
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/dudak/?page=9</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/dus-jeli/</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/el-kremi/</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/en-sevilenler/?page=10</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/en-sevilenler/?page=11</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/en-sevilenler/?page=12</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/en-sevilenler/?page=3</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/en-sevilenler/?page=4</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/en-sevilenler/?page=5</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/en-sevilenler/?page=6</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/en-sevilenler/?page=7</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/en-sevilenler/?page=8</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/en-sevilenler/?page=9</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/extreme-tattoo-family/?page=2</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/extreme-tattoo-uzun-sure-sabitleyici-etkili-transparan-jel-kas-wax-i-beyaz-8682536110471/</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/firsat-urunleri/?page=3</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/firsat-urunleri/?page=4</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/firsat-urunleri/?page=5</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/fondoten/?page=3</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/fondoten/?page=4</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/fondoten/?page=5</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-beyaz-8690604310371/</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-bordo-8690604379934/</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-bordo-8690604593231/</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-kahverengi-8690604310470/</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-kahverengi-8690604379965/</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-kahverengi-8690604379972/</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-kirmizi-8690604310456/</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-kirmizi-8690604497652/</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-mor-8690604310654/</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-mor-8690604379910/</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-mor-8690604497669/</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-pembe-8690604310388/</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-pembe-8690604310395/</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-pembe-8690604497591/</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-pembe-8690604528585/</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-siyah-8690604310661/</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-siyah-8690604313228/</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-yesil-8690604310593/</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color-ultra-yuksek-pigmentli-parlak-bitisli-oje-yesil-8690604310609/</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color/?page=2</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/glow-lip-oil-nemlendirici-etkili-isiltili-bitisli-renkli-dudak-yagi-pembe-8682536104074/</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/goz-fari/?page=3</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/goz-fari/?page=4</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/goz-makyaji/?page=10</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/goz-makyaji/?page=4</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/goz-makyaji/?page=5</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/goz-makyaji/?page=6</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/goz-makyaji/?page=7</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/goz-makyaji/?page=8</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/goz-makyaji/?page=9</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/gunes-koruyucu-fondoten/?page=3</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/hande-ercelin-favorileri/?page=3</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/hd-weightless-yuksek-pigmentli-mat-bitisli-kremsi-hafif-ruj-kahverengi-8690604518715/</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/hd-weightless-yuksek-pigmentli-mat-bitisli-kremsi-hafif-ruj-pembe-8690604648719/</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/hd-weightless-yuksek-pigmentli-mat-bitisli-kremsi-hafif-ruj-pembe-8690604648726/</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/helal-sertifikasi/</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/higloss-uzun-sure-parlaklik-sunan-yuksek-performansli-isiltili-bitisli-oje-bej-8682536119580/</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/higloss-uzun-sure-parlaklik-sunan-yuksek-performansli-isiltili-bitisli-oje-bordo-8682536119726/</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/higloss-uzun-sure-parlaklik-sunan-yuksek-performansli-isiltili-bitisli-oje-kirmizi-8682536119689/</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/higloss-uzun-sure-parlaklik-sunan-yuksek-performansli-isiltili-bitisli-oje-kirmizi-8682536119702/</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/higloss-uzun-sure-parlaklik-sunan-yuksek-performansli-isiltili-bitisli-oje-mavi-8682536119764/</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/higloss-uzun-sure-parlaklik-sunan-yuksek-performansli-isiltili-bitisli-oje-pembe-8682536119627/</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/higloss-uzun-sure-parlaklik-sunan-yuksek-performansli-isiltili-bitisli-oje-pembe-8682536119641/</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/higloss-uzun-sure-parlaklik-sunan-yuksek-performansli-isiltili-bitisli-oje-yesil-8682536119740/</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/indirim-firsati-urunleri/?page=10</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/indirim-firsati-urunleri/?page=11</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/indirim-firsati-urunleri/?page=12</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/indirim-firsati-urunleri/?page=3</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/indirim-firsati-urunleri/?page=4</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/indirim-firsati-urunleri/?page=5</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/indirim-firsati-urunleri/?page=6</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/indirim-firsati-urunleri/?page=7</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/indirim-firsati-urunleri/?page=8</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/indirim-firsati-urunleri/?page=9</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/invisible-cover-hd-hafif-yapili-yari-parlak-bitisli-spf30-fondoten-bej-8682536059053/</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/invisible-cover-hd-hafif-yapili-yari-parlak-bitisli-spf30-fondoten-bej-8682536059091/</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/invisible-cover-hd-hafif-yapili-yari-parlak-bitisli-spf30-fondoten-bej-8682536059114/</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/invisible-cover-hd-hafif-yapili-yari-parlak-bitisli-spf30-fondoten-bej-8682536059152/</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/invisible-cover-hd-hafif-yapili-yari-parlak-bitisli-spf30-fondoten-bej-8682536059176/</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/invisible-cover-hd-hafif-yapili-yari-parlak-bitisli-spf30-fondoten-pembe-8682536059015/</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/invisible-cover-hd-hafif-yapili-yari-parlak-bitisli-spf30-fondoten-pembe-8682536059077/</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/invisible-cover-hd-hafif-yapili-yari-parlak-bitisli-spf30-fondoten-pembe-8682536059138/</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/iyi-uretim-uygulamalari-sertifikasi/</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/jel-oje/?page=3</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/jelly-look-yuksek-pigmentli-parlak-bitisli-jel-gorunumlu-oje-gri-8690604497744/</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/jelly-look-yuksek-pigmentli-parlak-bitisli-jel-gorunumlu-oje-mavi-8690604233670/</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/jelly-look-yuksek-pigmentli-parlak-bitisli-jel-gorunumlu-oje-pembe-8690604233649/</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/jelly-look-yuksek-pigmentli-parlak-bitisli-jel-gorunumlu-oje-pembe-8690604378432/</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/jelly-look-yuksek-pigmentli-parlak-bitisli-jel-gorunumlu-oje-yesil-8682536023245/</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/jelly-look/?page=2</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/k-spirit-collection/?page=2</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/k-spirit-lip-mask-ultra-nemlendirici-ve-besleyici-dudak-maskesi-kirmizi-8682536107594/</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/k-spirit-lip-mask-ultra-nemlendirici-ve-besleyici-dudak-maskesi-mavi-8682536107600/</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/k-spirit-lip-mask-ultra-nemlendirici-ve-besleyici-dudak-maskesi-mor-8682536107617/</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/k-spirit-moussy-lip-cheek-yogunlugu-ayarlanabilir-dudak-ve-yanak-renklendiricisi-kiremit-8682536111294/</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/k-spirit-moussy-lip-cheek-yogunlugu-ayarlanabilir-dudak-ve-yanak-renklendiricisi-kirmizi-8682536111300/</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/k-spirit-moussy-lip-cheek-yogunlugu-ayarlanabilir-dudak-ve-yanak-renklendiricisi-pembe-8682536111287/</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/kiss-me-more-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-mor-8682536040907/</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/kiss-me-more-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-pembe-8682536040693/</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/kiss-me-more-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-pembe-8682536040815/</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/kiss-me-more-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-pembe-8682536040877/</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/kiss-me-more-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-pembe-8682536040884/</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/kova-burcu-3-lu-makyaj-seti-renkli-set111/</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/kremsi-dokulu-mat-bitisli-isiltili-9-lu-kompakt-goz-fari-paleti-bej-kahverengi-yesil-turuncu-8682536121170/</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/kvkk/</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/latte-besleyici-etkili-kahve-aromali-dudak-parlaticisi-pembe-bronze-8682536100588/</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/latte-kahve-tonlari-3-lu-oje-seti-set304/</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/latte-koleksiyonu/?page=2</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-lip-powder-yuksek-pigmentli-mat-bitisli-ultra-hafif-ruj-kahverengi-8682536061728/</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-lip-powder-yuksek-pigmentli-mat-bitisli-ultra-hafif-ruj-kahverengi-8682536061766/</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-lip-powder-yuksek-pigmentli-mat-bitisli-ultra-hafif-ruj-pembe-8682536061681/</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-lip-powder-yuksek-pigmentli-mat-bitisli-ultra-hafif-ruj-pembe-8682536061704/</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-lip-powder-yuksek-pigmentli-mat-bitisli-ultra-hafif-ruj-pembe-8682536061742/</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-lip-powder-yuksek-pigmentli-mat-bitisli-ultra-hafif-ruj-pembe-8682536061780/</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-lip-powder-yuksek-pigmentli-mat-bitisli-ultra-hafif-ruj-pembe-8682536061803/</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-lip-powder-yuksek-pigmentli-mat-bitisli-ultra-hafif-ruj-pembe-8682536061827/</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-lip-powder-yuksek-pigmentli-mat-bitisli-ultra-hafif-ruj-pembe-8682536061841/</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-lip-powder-yuksek-pigmentli-mat-bitisli-ultra-hafif-ruj-pembe-8682536061940/</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-yari-transparan-mat-bitisli-nemlendirici-dudak-pudrasi-kirmizi-8682536094375/</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-yari-transparan-mat-bitisli-nemlendirici-dudak-pudrasi-kirmizi-8682536094399/</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-yari-transparan-mat-bitisli-nemlendirici-dudak-pudrasi-mor-8682536048873/</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-yari-transparan-mat-bitisli-nemlendirici-dudak-pudrasi-mor-8682536048910/</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-yari-transparan-mat-bitisli-nemlendirici-dudak-pudrasi-mor-8682536094436/</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-yari-transparan-mat-bitisli-nemlendirici-dudak-pudrasi-pembe-8682536094252/</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-yari-transparan-mat-bitisli-nemlendirici-dudak-pudrasi-seftali-8682536094276/</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-yari-transparan-mat-bitisli-nemlendirici-dudak-pudrasi-turuncu-8682536048859/</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/likit-kapatici/?page=2</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/likit-ruj/?page=2</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lip-cheek-yuksek-pigmentli-kremsi-yari-mat-bitisli-crayon-gul-kurusu-8682536121477/</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lip-cheek-yuksek-pigmentli-kremsi-yari-mat-bitisli-crayon-kahverengi-8682536121538/</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lip-cheek-yuksek-pigmentli-kremsi-yari-mat-bitisli-crayon-kiremit-8682536121491/</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lip-cheek-yuksek-pigmentli-kremsi-yari-mat-bitisli-crayon-kirmizi-8682536121552/</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lip-cheek-yuksek-pigmentli-kremsi-yari-mat-bitisli-crayon-mor-8682536121453/</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lip-cheek-yuksek-pigmentli-kremsi-yari-mat-bitisli-crayon-pembe-8682536121514/</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lip-perfection-primer-nemlendirici-etkili-uzun-sure-kalici-dudak-makyaji-bazi-transparan-8682536100137/</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/makyaj-setleri/?page=4</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/makyaj-setleri/?page=5</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/makyaj-setleri/?page=6</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/makyaj/?page=2</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mat-ruj/?page=3</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mat-ruj/?page=4</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mat-ruj/?page=5</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mediterranean-akdeniz-esintisi-3-lu-oje-seti-set302/</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mediterranean-yaz-renkleri-3-lu-oje-seti-set303/</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mediterranean-yuksek-pigmentli-parlak-bitisli-oje-040-soft-beige-8682536113373/</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mediterranean-yuksek-pigmentli-parlak-bitisli-oje-acik-mavi-8682536113298/</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mediterranean-yuksek-pigmentli-parlak-bitisli-oje-acik-pembe-8682536113434/</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mediterranean-yuksek-pigmentli-parlak-bitisli-oje-kirmizi-8682536113397/</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mediterranean-yuksek-pigmentli-parlak-bitisli-oje-koyu-yesil-8682536113274/</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mediterranean-yuksek-pigmentli-parlak-bitisli-oje-lacivert-8682536113311/</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mediterranean-yuksek-pigmentli-parlak-bitisli-oje-lila-8682536113212/</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mediterranean-yuksek-pigmentli-parlak-bitisli-oje-pembe-8682536113335/</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mediterranean-yuksek-pigmentli-parlak-bitisli-oje-pembe-8682536113410/</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mediterranean-yuksek-pigmentli-parlak-bitisli-oje-sari-8682536113236/</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mediterranean-yuksek-pigmentli-parlak-bitisli-oje-turuncu-8682536113359/</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/metaglam-yogun-isiltili-nemlendirici-etkili-yari-transparan-dudak-parlaticisi-pembe-8682536080811/</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/metaglam-yuksek-pigmentli-mat-bitisli-kremsi-kompakt-allik-kirmizi-8682536080675/</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/metaglam-yuksek-pigmentli-mat-bitisli-kremsi-kompakt-allik-pembe-8682536095983/</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-bej-8682536108430/</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-bordo-8682536108812/</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-kahverengi-8682536108775/</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-kahverengi-8682536108973/</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-kirmizi-8682536095631/</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-mavi-8682536108911/</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-pembe-8682536108515/</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-pembe-8682536108591/</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-pembe-8682536108898/</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-pembe-altin-8682536095594/</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-turuncu-8682536108553/</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-turuncu-8682536108874/</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-yesil-8682536095617/</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/nail-enamel/?page=2</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/nemlendirici-fondoten/?page=2</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/oje/?page=10</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/oje/?page=3</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/oje/?page=4</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/oje/?page=5</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/oje/?page=6</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/oje/?page=7</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/oje/?page=8</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/oje/?page=9</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/parlak-fondoten/?page=2</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/pearly-yari-transparan-parlak-bitisli-sedefli-oje-gri-8682536109963/</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/pearly-yari-transparan-parlak-bitisli-sedefli-oje-mavi-8682536109987/</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/pembe-oje/?page=2</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/pembe-ruj/?page=2</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/perfect-eyes-4-lu-goz-makyaji-seti-renkli-set122/</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sadece-flormarda-urunleri/?page=10</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sadece-flormarda-urunleri/?page=11</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sadece-flormarda-urunleri/?page=12</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sadece-flormarda-urunleri/?page=3</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sadece-flormarda-urunleri/?page=4</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sadece-flormarda-urunleri/?page=5</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sadece-flormarda-urunleri/?page=6</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sadece-flormarda-urunleri/?page=7</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sadece-flormarda-urunleri/?page=8</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sadece-flormarda-urunleri/?page=9</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/shine-kiss-me-more-uzun-sure-kalici-parlak-bitisli-likit-ruj-pembe-8682536083676/</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/shine-kiss-me-more-uzun-sure-kalici-parlak-bitisli-likit-ruj-pembe-8682536083775/</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/shine-kiss-me-more-uzun-sure-kalici-parlak-bitisli-likit-ruj-pembe-8682536083799/</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/shine-kiss-me-more-uzun-sure-kalici-parlak-bitisli-likit-ruj-pembe-8682536083836/</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/shine-kiss-me-more-uzun-sure-kalici-parlak-bitisli-likit-ruj-pembe-8682536083850/</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/shine-kiss-me-more-uzun-sure-kalici-parlak-bitisli-likit-ruj-pembe-8682536083874/</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/shine-kiss-me-more-uzun-sure-kalici-parlak-bitisli-likit-ruj-seftali-8682536083690/</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/shine-kiss-me-more-uzun-sure-kalici-parlak-bitisli-likit-ruj-seftali-8682536083713/</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/shine-kiss-me-more-uzun-sure-kalici-parlak-bitisli-likit-ruj-turuncu-8682536083812/</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/silk-matte-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-bordo-8682536076616/</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/silk-matte-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-kahverengi-8682536032896/</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/silk-matte-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-kiremit-8682536076609/</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/silk-matte-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-kirmizi-8682536076647/</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/silk-matte-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-mor-8690604505425/</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/silk-matte-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-pembe-8682536033008/</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/silk-matte-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-pembe-8690604397358/</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/silk-matte-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-pembe-8690604627615/</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/silk-matte-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-pembe-8690604627622/</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/silk-matte-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-seftali-8682536076623/</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/silk-matte-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-seftali-8682536076630/</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/silk-matte-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-ten-rengi-8682536076685/</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sitemaps/sitemap-categories-1.xml.gz</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>Alt kırılım</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sitemaps/sitemap-flatpages-1.xml.gz</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>Alt kırılım</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sitemaps/sitemap-products-1.xml.gz</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>Alt kırılım</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sitemaps/sitemap-specialpages-1.xml.gz</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>Alt kırılım</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/skin-lifting-sikilastirici-bakim-yapan-kremsi-dokulu-spf-30-fondoten-bej-8682536059596/</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/skin-lifting-sikilastirici-bakim-yapan-kremsi-dokulu-spf-30-fondoten-bej-8682536059671/</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C287" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/skin-lifting-sikilastirici-bakim-yapan-kremsi-dokulu-spf-30-fondoten-bej-8682536059756/</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/skin-lifting-sikilastirici-bakim-yapan-kremsi-dokulu-spf-30-fondoten-bej-8682536059770/</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/skin-lifting-sikilastirici-bakim-yapan-kremsi-dokulu-spf-30-fondoten-bej-8682536059794/</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/skin-lifting-sikilastirici-bakim-yapan-kremsi-dokulu-spf-30-fondoten-kahverengi-8682536059817/</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/skin-lifting-sikilastirici-bakim-yapan-kremsi-dokulu-spf-30-fondoten-pembe-8682536059732/</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C292" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/star-shine-yuksek-pigmentli-parlak-bitisli-metalik-oje-altin-8682536115100/</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/stylematic-mat-bitisli-suya-dayanikli-asansorlu-dudak-kalemi-bej-8682536039215/</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/stylematic-mat-bitisli-suya-dayanikli-asansorlu-dudak-kalemi-kahverengi-8682536039246/</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/stylematic-mat-bitisli-suya-dayanikli-asansorlu-dudak-kalemi-kahverengi-8682536039260/</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/stylematic-mat-bitisli-suya-dayanikli-asansorlu-dudak-kalemi-kahverengi-8690604497058/</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/stylematic-mat-bitisli-suya-dayanikli-asansorlu-dudak-kalemi-kahverengi-8690604497065/</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C298" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/stylematic-mat-bitisli-suya-dayanikli-asansorlu-dudak-kalemi-kahverengi-8690604497072/</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/stylematic-mat-bitisli-suya-dayanikli-asansorlu-dudak-kalemi-mor-8690604497089/</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/stylematic-mat-bitisli-suya-dayanikli-asansorlu-dudak-kalemi-pembe-8682536039222/</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/stylematic-mat-bitisli-suya-dayanikli-asansorlu-dudak-kalemi-pembe-8682536039239/</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C302" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/terazi-burcu-3-lu-makyaj-seti-renkli-set108/</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C303" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tirnak/?page=10</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tirnak/?page=3</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tirnak/?page=4</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tirnak/?page=5</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tirnak/?page=6</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tirnak/?page=7</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tirnak/?page=8</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tirnak/?page=9</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/to-go-isiltili-dogal-bitisli-yogunlugu-ayarlanabilir-kremsi-stick-allik-murdum-8682536098496/</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C312" s="3" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/toz-pudra/?page=2</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tum-urunler/?page=12</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C314" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tum-urunler/?page=13</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tum-urunler/?page=14</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C316" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tum-urunler/?page=15</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C317" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tum-urunler/?page=16</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C318" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tum-urunler/?page=17</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C319" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tum-urunler/?page=18</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C320" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tum-urunler/?page=3</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tum-urunler/?page=4</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C322" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tum-urunler/?page=5</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C323" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tum-urunler/?page=6</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C324" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tum-urunler/?page=7</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C325" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tum-urunler/?page=8</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C326" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tum-urunler/?page=9</t>
+        </is>
+      </c>
+      <c r="B327" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C327" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/yilbasi-indirimleri/?page=2</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C328" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/yuz-makyaji/?page=10</t>
+        </is>
+      </c>
+      <c r="B329" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C329" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/yuz-makyaji/?page=11</t>
+        </is>
+      </c>
+      <c r="B330" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C330" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/yuz-makyaji/?page=12</t>
+        </is>
+      </c>
+      <c r="B331" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C331" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/yuz-makyaji/?page=13</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C332" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/yuz-makyaji/?page=3</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C333" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/yuz-makyaji/?page=4</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C334" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/yuz-makyaji/?page=5</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C335" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/yuz-makyaji/?page=6</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C336" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/yuz-makyaji/?page=7</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/yuz-makyaji/?page=8</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C338" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/yuz-makyaji/?page=9</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C339" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="5" t="inlineStr">
+        <is>
+          <t>NOT: Listedeki tek 404 kaydında bağlantı adresine boşluk karakteri ve ikinci bir adres yapışmıştır; kaynak sayfadaki bağlantı düzeltilmelidir. Kalan 337 kayıt 405 yanıtıdır ve site hatası değildir: örneklenen 16 adres normal tarayıcı isteğinde 200 yanıtı vermiş, ayrı bir kontrolde Googlebot, GPTBot, OAI-SearchBot, PerplexityBot ve ClaudeBot kullanıcı ajanlarının tamamı 200 almıştır. Kayıtlar yoğun paralel taramaya karşı uygulanan hız sınırı olarak değerlendirilmiştir; sistematik bir erişim engeli tespit edilmemiştir.</t>
         </is>
       </c>
     </row>
@@ -2304,6 +6806,247 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="78" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Sayfa tipi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/stay-perfect-concealer-corrector/</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sadece-flormarda-urunleri/?page=2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/users/auth/</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Alt kırılım</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/hande-ercelin-favorileri/</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/latte-koleksiyonu/</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/1-alana-1-hediye/</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/ayin-firsat-urunleri/</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/cerezlere-iliskin-aydinlatma-metni/</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/indirim-firsati-urunleri/?page=2</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sadece-flormarda-urunleri/</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/users/password/reset/</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Alt kırılım</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/hande-ercelin-favorileri/?page=2</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/vintage-romance-nail-enamel/</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sheer-up-intense-urunleri/</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sheer-up-rujlar/?page=2</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/indirim-firsati-urunleri/</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sheer-up-rujlar/</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>NOT: A sütunundaki sayfada meta description bulunmamaktadır; kampanya, koleksiyon ve üyelik şablonlarına sayfa içeriğini özetleyen bir açıklama eklenmelidir. Liste JavaScript rendering açık taramaya aittir; render'sız taramada bu kalem 884 sayfa olarak raporlanmakta, aradaki fark açıklamanın render sonrası oluşmasından kaynaklanmaktadır.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2466,7 +7209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3941,7 +8684,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>NOT: A sütunundaki URL'lerden 7'si sitemap dosyalarında yer aldığı halde 500 yanıtı vermektedir; yayından kaldırılacaklar sitemap'ten çıkarılmalı, açık kalacaklar için sunucu hatası giderilmelidir. 502 yanıtı veren kayıtların tamamı yüksek numaralı pagination sayfasıdır (?page=19 ve üzeri); pagination'ın derin sayfalarında sunucu tarafı incelenmelidir.</t>
+          <t>NOT: Liste 3 Ağu 2026 tarihli Ahrefs Site Audit taramasına aittir. A sütunundaki URL'lerden 7'si sitemap dosyalarında yer aldığı halde 500 yanıtı vermektedir; yayından kaldırılacaklar sitemap'ten çıkarılmalı, açık kalacaklar için sunucu hatası giderilmelidir. 502 yanıtı veren kayıtların tamamı yüksek numaralı pagination sayfasıdır (?page=19 ve üzeri). 12 Ağu 2026 tarihli, JavaScript rendering açık site geneli taramada 5XX yanıtı görülmemiştir; listedeki kayıtların güncel durumu tek tek doğrulanmalıdır.</t>
         </is>
       </c>
     </row>
@@ -4193,12 +8936,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4221,109 +8964,568 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/gloss-define-makyaj-seti-pembe-set057/</t>
+          <t>https://www.flormar.com.tr/velvet-rose-pembe-tonlu-3-lu-dudak-seti-pembe-set203/</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Gloss&amp; Define Makyaj Seti | Flormar</t>
+          <t>Velvet Rose Pembe Tonlu 3'lü Dudak Seti | Flormar</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Flormar Ürünleri</t>
+          <t>Velvet Rose Pembe Tonlu 3'lü Dudak Seti</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/pink-elegant-shades-3-lu-oje-seti-pembe-set058/</t>
+          <t>https://www.flormar.com.tr/espresso-shine-kahve-tonlu-3-lu-dudak-seti-kahverengi-set204/</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Pink Elegant Shades 3'lü Oje Seti | Flormar</t>
+          <t>Espresso Shine Kahve Tonlu 3'lü Dudak Seti | Flormar</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Flormar Ürünleri</t>
+          <t>Espresso Shine Kahve Tonlu 3'lü Dudak Seti</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/all-time-favorites-5-li-oje-seti-renkli-set059/</t>
+          <t>https://www.flormar.com.tr/mix-match-2-li-aydinlatici-allik-seti-pembe-set135/</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>All Time Favorites 5'li Oje Seti | Flormar</t>
+          <t>Mix &amp; Match 2'li Aydınlatıcı&amp;Allık Seti | Flormar</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Flormar Ürünleri</t>
+          <t>Mix &amp; Match 2'li Aydınlatıcı &amp; Allık Set&lt;span class="dots"&gt;...&lt;/span&gt;</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/bridal-6-li-oje-seti-renkli-set078/</t>
+          <t>https://www.flormar.com.tr/ultimate-favorites-makyaj-seti-renkli-set070/</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Bridal 6'lı Oje Seti | Flormar</t>
+          <t>Ultimate Favorites Makyaj Seti | Flormar</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Bridal 6'lı Oje Seti</t>
+          <t>Ultimate Favorites Makyaj Seti</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/coveted-classics-trio-makyaj-seti-renkli-set067/</t>
+          <t>https://www.flormar.com.tr/oglak-burcu-3-lu-makyaj-seti-renkli-set110/</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Coveted Classics Trio Makyaj Seti | Flormar</t>
+          <t>Oğlak Burcu 3'lü Makyaj Seti | Flormar</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Flormar Ürünleri</t>
+          <t>Oğlak Burcu 3'lü Makyaj Seti</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>https://www.flormar.com.tr/kiss-the-year-3-lu-makyaj-seti-kirmizi-set143/</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Kiss the Year 3'lü Makyaj Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Kiss the Year 3'lü Makyaj Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/cheers-to-nails-3-lu-oje-seti-set142/</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Cheers to Nails 3'lü Oje Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Cheers to Nails 3'lü Oje Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/juicy-lips-3-lu-dudak-seti-renkli-set207/</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Juicy Lips 3'lu Dudak Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Juicy Lips 3'lü Dudak Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/treasure-lashes-2-li-goz-makyaji-seti-renkli-set209/</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Treasure Lashes 2'li Göz Makyajı Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Treasure Lashes 2'li Göz Makyajı Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/strawberry-makeup-4-lu-makyaj-seti-renkli-set086/</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Strawberry Makeup 4'lü Makyaj Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Strawberry Makeup 4'lü Makyaj Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/bridal-6-li-oje-seti-renkli-set078/</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Bridal 6'lı Oje Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Bridal 6'lı Oje Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>https://www.flormar.com.tr/shinny-peach-3-lu-makyaj-seti-renkli-set099/</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Shinny Peach 3'lü Makyaj Seti | Flormar</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Shinny Peach 3'lü Makyaj Seti</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>NOT: A sütunundaki sayfada birden fazla title etiketi bulunmaktadır; sayfa başına tek ve benzersiz title kalacak şekilde düzeltilmelidir. C sütunundaki ikinci başlık set ve ürün şablonundaki bir modül çıktısından gelmektedir, düzeltme şablon düzeyinde yapılmalıdır.</t>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/pretty-in-pink-kit-makyaj-seti-pembe-set064/</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Pretty in Pink Kit Makyaj Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Ürünleri</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/meyve-ozleriyle-renkli-dudaklar-2-li-lip-balm-tint-seti-pembe-set139/</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Meyve Özleriyle Renkli Dudaklar 2'li Lip Balm&amp;Tint Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Meyve Özleriyle Renkli Dudaklar 2'li Lip&lt;span class="dots"&gt;...&lt;/span&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/all-time-favorites-5-li-oje-seti-renkli-set059/</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>All Time Favorites 5'li Oje Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Ürünleri</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/hafif-yaz-makyaji-3-lu-makyaj-seti-renkli-set188/</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Hafif Yaz Makyajı 3'lü Makyaj Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Hafif Yaz Makyajı 3'lü Makyaj Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/beklemeyi-sevmeyenlere-hizli-kuruyan-5-li-oje-seti-renkli-set140/</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Beklemeyi Sevmeyenlere Hızlı Kuruyan 5'li Oje Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Beklemeyi Sevmeyenlere Hızlı Kuruyan 5'l&lt;span class="dots"&gt;...&lt;/span&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/the-lip-ritual-3-lu-dudak-makyaji-seti-renkli-set212/</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>The Lip Ritual 3'lü Dudak Makyajı Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>The Lip Ritual 3'lü Dudak Makyajı Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/iconic-selection-makyaj-seti-renkli-set056/</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Iconic Selection Makyaj Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Ürünleri</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/duo-delight-makyaj-seti-renkli-set068/</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Duo Delight Makyaj Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Ürünleri</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/glow-getter-4-lu-makyaj-seti-renkli-set061/</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Glow Getter 4'lü Makyaj Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Ürünleri</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/pratik-4-lu-makyaj-seti-renkli-set191/</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Pratik 4'lü Makyaj Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Pratik 4'lü Makyaj Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mat-smooth-2-li-dudak-seti-renkli-set208/</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Mat &amp; Smooth 2'li Dudak Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Mat &amp; Smooth 2'li Dudak Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/suya-dayanikli-3-lu-goz-makyaji-seti-renkli-set048/</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Suya Dayanıklı 3'lü Göz Makyajı Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Ürünleri</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lift-up-dolgun-gorunum-veren-2-li-kirmizi-dudak-seti-kirmizi-set195/</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Lift Up Dolgun Görünüm Veren 2'li Kırmızı Dudak Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Lift Up Kırmızı 2'li Dudak Kombosu</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/pink-elegant-shades-3-lu-oje-seti-pembe-set058/</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Pink Elegant Shades 3'lü Oje Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Ürünleri</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/summer-jam-4-lu-makyaj-seti-renkli-set079/</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Summer Jam 4'lü Makyaj Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Summer Jam 4'lü Makyaj Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lift-up-dolgun-gorunum-veren-2-li-nude-dudak-seti-kahverengi-set196/</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Lift Up Dolgun Görünüm Veren 2'li Nude Dudak Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Lift Up Doğal Görünümlü 2'li Dudak Kombosu</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/hydra-radiance-2-li-yuz-makyaji-seti-renkli-set210/</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Hydra Radiance 2'li Yüz Makyajı Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Hydra Radiance 2'li Yüz Makyajı Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/signature-selection-makyaj-seti-renkli-set069/</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Signature Selection Makyaj Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Signature Selection Makyaj Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/gloss-define-makyaj-seti-pembe-set057/</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Gloss&amp; Define Makyaj Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Ürünleri</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/coveted-classics-trio-makyaj-seti-renkli-set067/</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Coveted Classics Trio Makyaj Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Ürünleri</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/basak-burcu-3-lu-makyaj-seti-renkli-set107/</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Başak Burcu 3'lü Makyaj Seti | Flormar</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Başak Burcu 3'lü Makyaj Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>NOT: A sütunundaki sayfada birden fazla title etiketi bulunmaktadır ve listedeki 33 kaydın tamamında ikinci title &lt;head&gt; bloğunun dışında, gövde içinde yer almaktadır; gövdedeki başlık etiketi kaldırılmalı, sayfa başına tek ve benzersiz title &lt;head&gt; içinde kalmalıdır. C sütunundaki ikinci başlık set ürün şablonundaki ürün adı çıktısından gelmektedir, düzeltme şablon düzeyinde yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -4338,7 +9540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -4360,72 +9562,72 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/</t>
+          <t>https://www.flormar.com.tr/stay-perfect-concealer-corrector/</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Anasayfa</t>
+          <t>Kategori</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/cok-satanlar/</t>
+          <t>https://www.flormar.com.tr/zodiac-burcuna-gore-oje/</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Listeleme</t>
+          <t>Kategori</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/ayin-firsat-urunleri/</t>
+          <t>https://www.flormar.com.tr/tum-urunler/?page=11</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Kampanya</t>
+          <t>Pagination</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/tirnak-cok-satanlar/</t>
+          <t>https://www.flormar.com.tr/tum-urunler/?page=10</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Listeleme</t>
+          <t>Pagination</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/dudak-cok-satanlar/</t>
+          <t>https://www.flormar.com.tr/sadece-flormarda-urunleri/?page=2</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Listeleme</t>
+          <t>Pagination</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/yuz-cok-satanlar/</t>
+          <t>https://www.flormar.com.tr/tum-urunler/?page=2</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Listeleme</t>
+          <t>Pagination</t>
         </is>
       </c>
     </row>
@@ -4437,194 +9639,494 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Listeleme</t>
+          <t>Kategori</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/sheer-up-intense-urunleri/</t>
+          <t>https://www.flormar.com.tr/users/auth/</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Koleksiyon</t>
+          <t>Alt kırılım</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/makyaj-gerecleri-cok-satanlar/</t>
+          <t>https://www.flormar.com.tr/hande-ercelin-favorileri/</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Listeleme</t>
+          <t>Kategori</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/sadece-flormarda-urunleri/</t>
+          <t>https://www.flormar.com.tr/latte-koleksiyonu/</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Koleksiyon</t>
+          <t>Kategori</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/firsat-urunleri/</t>
+          <t>https://www.flormar.com.tr/</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Kampanya</t>
+          <t>Anasayfa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/sheer-up-rujlar/</t>
+          <t>https://www.flormar.com.tr/extreme-tattoo-family/</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Koleksiyon</t>
+          <t>Kategori</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/en-sevilenler/</t>
+          <t>https://www.flormar.com.tr/nail-enamel/</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Listeleme</t>
+          <t>Kategori</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/indirim-firsati-urunleri/</t>
+          <t>https://www.flormar.com.tr/yilbasi-indirimleri/</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Kampanya</t>
+          <t>Kategori</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/cilt-bakimi-cok-satanlar/</t>
+          <t>https://www.flormar.com.tr/dudak-cok-satanlar/</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Listeleme</t>
+          <t>Kategori</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/tum-urunler/</t>
+          <t>https://www.flormar.com.tr/cok-satanlar/?page=4</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Listeleme</t>
+          <t>Pagination</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/hande-ercelin-favorileri/</t>
+          <t>https://www.flormar.com.tr/cok-satanlar/?page=3</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Koleksiyon</t>
+          <t>Pagination</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/jelly-look/</t>
+          <t>https://www.flormar.com.tr/cok-satanlar/?page=2</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Koleksiyon</t>
+          <t>Pagination</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/1-alana-1-hediye/</t>
+          <t>https://www.flormar.com.tr/cok-satanlar/?page=8</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Kampanya</t>
+          <t>Pagination</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/yilbasi-indirimleri/</t>
+          <t>https://www.flormar.com.tr/cok-satanlar/?page=7</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Kampanya</t>
+          <t>Pagination</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/latte-koleksiyonu/</t>
+          <t>https://www.flormar.com.tr/cok-satanlar/?page=6</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Koleksiyon</t>
+          <t>Pagination</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/extreme-tattoo-family/</t>
+          <t>https://www.flormar.com.tr/cok-satanlar/?page=5</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Koleksiyon</t>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/cok-satanlar/</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>NOT: A sütunundaki sayfada H1 etiketi bulunmamaktadır; listeleme, kampanya ve koleksiyon şablonlarına sayfa başlığını taşıyan tek bir H1 eklenmelidir. Liste 12 Ağu taramasındaki 734 indekslenebilir sayfa kümesine aittir; geniş kapsamlı taramada (3.399 URL) bu sayı 1.416 olarak raporlandığından şablon bazında ayrıca doğrulanmalıdır.</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/firsat-urunleri/</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/matte-finish/</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/1-alana-1-hediye/</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/ayin-firsat-urunleri/</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/indirim-firsati-urunleri/?page=2</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sadece-flormarda-urunleri/</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tirnak-cok-satanlar/</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/full-color/</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/tum-urunler/</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/en-sevilenler/</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/cilt-bakimi-cok-satanlar/</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/users/password/reset/</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Alt kırılım</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/hande-ercelin-favorileri/?page=2</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/firsat-urunleri/?page=2</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/jelly-look/</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/k-spirit-collection/</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/vintage-romance-nail-enamel/</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sheer-up-intense-urunleri/</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sheer-up-rujlar/?page=2</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/indirim-firsati-urunleri/</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/en-sevilenler/?page=2</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/sheer-up-rujlar/</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/yuz-cok-satanlar/</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/makyaj-gerecleri-cok-satanlar/</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>NOT: A sütunundaki sayfada H1 etiketi bulunmamaktadır; anasayfa, listeleme, kampanya ve koleksiyon şablonlarına sayfa başlığını taşıyan tek bir H1 eklenmelidir. Liste 12 Ağu tarihli, JavaScript rendering açık site geneli taramasındaki 1.279 indekslenebilir sayfa kümesine aittir ve kayıtların tamamı indekslenebilir durumdadır.</t>
         </is>
       </c>
     </row>
@@ -4639,7 +10141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -4667,92 +10169,1401 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/flormar-kurumsal-hediye/</t>
+          <t>https://www.flormar.com.tr/velvet-rose-pembe-tonlu-3-lu-dudak-seti-pembe-set203/</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Kurumsal Hediyeler</t>
+          <t>Velvet Rose Pembe Tonlu 3'lü Dudak Seti</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Flormar Hediye Kutusu Çeşitleri</t>
+          <t>Velvet Rose Pembe Tonlu 3'lü Dudak Seti içer...</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/bridal-6-li-oje-seti-renkli-set078/</t>
+          <t>https://www.flormar.com.tr/lightweight-yari-transparan-mat-bitisli-nemlendirici-dudak-pudrasi-pembe-8682536094351/</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Bridal 6'lı Oje Seti</t>
+          <t>Lightweight Yarı Transparan &amp; Mat Bitişli Nemlendirici Dudak Pudrası</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Bridal 6'lı Oje Seti İçerisindeki Ürünler</t>
+          <t>Flormar Lightweight Yarı Transparan&amp;Mat Bitişli Nemlendirici Dudak Pudrası</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/dewy-lip-glaze-parlak-dolgun-gorunum-veren-yapismayan-dudak-parlaticisi-mercan-8682536069441/</t>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-gri-8682536108652/</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Dewy Lip Glaze Parlak &amp; Dolgun Görünüm Veren Yapışmayan Dudak Parlatıcısı</t>
+          <t>Mono Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Flormar Dewy Lip Glaze Nemlendirici Etkili Yarı Transparan Dudak Parlatıcısı</t>
+          <t>Flormar Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/lightweight-yari-transparan-mat-bitisli-nemlendirici-dudak-pudrasi-pembe-8682536094290/</t>
+          <t>https://www.flormar.com.tr/dewy-lip-glaze-parlak-dolgun-gorunum-veren-yapismayan-dudak-parlaticisi-pembe-8682536069489/</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Lightweight Yarı Transparan &amp; Mat Bitişli Nemlendirici Dudak Pudrası</t>
+          <t>Dewy Lip Glaze Parlak &amp; Dolgun Görünüm Veren Yapışmayan Dudak Parlatıcısı</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Flormar Lightweight Yarı Transparan&amp;Mat Bitişli Nemlendirici Dudak Pudrası</t>
+          <t>Flormar Dewy Lip Glaze Nemlendirici Etkili Yarı Transparan Dudak Parlatıcısı</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>https://www.flormar.com.tr/espresso-shine-kahve-tonlu-3-lu-dudak-seti-kahverengi-set204/</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Espresso Shine Kahve Tonlu 3'lü Dudak Seti</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Espresso Shine Kahve Tonlu 3'lü Dudak Set...</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-yari-transparan-mat-bitisli-nemlendirici-dudak-pudrasi-lila-8682536048835/</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Lightweight Yarı Transparan &amp; Mat Bitişli Nemlendirici Dudak Pudrası</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Lightweight Yarı Transparan&amp;Mat Bitişli Nemlendirici Dudak Pudrası</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/color-palette-ince-yapili-mat-bitisli-isiltili-4-lu-goz-fari-paleti-bej-bronz-kahverengi-8682536121231/</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Color Palette İnce Yapılı &amp; Mat Bitişli/Işıltılı 4'lü Göz Farı Paleti</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Color Palette İnce Yapılı &amp; Doğal Işıltılı 4'lü Kompakt Göz Farı Paleti</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/dewy-lip-glaze-parlak-dolgun-gorunum-veren-yapismayan-dudak-parlaticisi-pembe-8682536068277/</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Dewy Lip Glaze Parlak &amp; Dolgun Görünüm Veren Yapışmayan Dudak Parlatıcısı</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Dewy Lip Glaze Nemlendirici Etkili Yarı Transparan Dudak Parlatıcısı 014</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-pembe-8682536108577/</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Mono Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/dewy-lip-glaze-parlak-dolgun-gorunum-veren-yapismayan-dudak-parlaticisi-bej-8682536068031/</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Dewy Lip Glaze Parlak &amp; Dolgun Görünüm Veren Yapışmayan Dudak Parlatıcısı</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Dewy Lip Glaze Nemlendirici Etkili Yarı Transparan Dudak Parlatıcısı 002</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/dewy-lip-glaze-parlak-dolgun-gorunum-veren-yapismayan-dudak-parlaticisi-pembe-8682536068253/</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Dewy Lip Glaze Parlak &amp; Dolgun Görünüm Veren Yapışmayan Dudak Parlatıcısı</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Dewy Lip Glaze Nemlendirici Etkili Yarı Transparan Dudak Parlatıcısı 013</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/baked-blush-on-yuksek-pigmentli-dogal-isiltili-firinlanmis-allik-pembe-8682536080286/</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Baked Blush-On Yüksek Pigmentli &amp; Doğal Işıltılı Fırınlanmış Allık</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Baked Blush-On Yüksek Pigmentli &amp; Doğal Işıltılı Fırınlanmış Allık</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-yari-transparan-mat-bitisli-nemlendirici-dudak-pudrasi-pembe-8682536094313/</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Lightweight Yarı Transparan &amp; Mat Bitişli Nemlendirici Dudak Pudrası</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Lightweight Yarı Transparan&amp;Mat Bitişli Nemlendirici Dudak Pudrası</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/baked-blush-on-yuksek-pigmentli-dogal-isiltili-firinlanmis-allik-pembe-8682536080262/</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Baked Blush-On Yüksek Pigmentli &amp; Doğal Işıltılı Fırınlanmış Allık</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Baked Blush-On Yüksek Pigmentli &amp; Doğal Işıltılı Fırınlanmış Allık</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/wet-dry-mat-bitisli-kremsi-kompakt-pudra-bej-8682536053730/</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Wet &amp; Dry Mat Bitişli Kremsi Kompakt Pudra</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Wet &amp; Dry Mat Bitişli Kremsi Kompakt Pudra</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mix-match-2-li-aydinlatici-allik-seti-pembe-set135/</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Mix &amp; Match 2'li Aydınlatıcı&amp;Allık Seti</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Mix &amp; Match 2'li Aydınlatıcı &amp; Allık Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-mor-8682536108638/</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Mono Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-turuncu-8682536095655/</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Mono Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/dewy-lip-glaze-parlak-dolgun-gorunum-veren-yapismayan-dudak-parlaticisi-seftali-8682536068079/</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Dewy Lip Glaze Parlak &amp; Dolgun Görünüm Veren Yapışmayan Dudak Parlatıcısı</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Dewy Lip Glaze Nemlendirici Etkili Yarı Transparan Dudak Parlatıcısı 004</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/ultimate-favorites-makyaj-seti-renkli-set070/</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Ultimate Favorites Makyaj Seti</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Set içerisindeki ürünler:</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/oglak-burcu-3-lu-makyaj-seti-renkli-set110/</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Oğlak Burcu 3'lü Makyaj Seti</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Oğlak Burcu 3'lü Makyaj Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/wet-dry-mat-bitisli-kremsi-kompakt-pudra-kahverengi-8682536053754/</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Wet &amp; Dry Mat Bitişli Kremsi Kompakt Pudra</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Wet &amp; Dry Mat Bitişli Kremsi Kompakt Pudra</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/kiss-the-year-3-lu-makyaj-seti-kirmizi-set143/</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Kiss the Year 3'lü Makyaj Seti</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Kiss the Year 3'lü Makyaj Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/kiss-me-more-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-pembe-8682536040853/</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Kiss Me More Yüksek Pigmentli &amp; Mat Bitişli Nemlendirici Likit Ruj</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Kiss Me More Yüksek Pigmentli &amp; Mat Bitişli Nemlendirici Likit Ruj 018</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
           <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-gumus-8682536095679/</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Mono Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Flormar Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>NOT: A sütunundaki sayfada birden fazla H1 etiketi bulunmaktadır; ikinci başlık H2 seviyesine indirilmelidir. Geniş kapsamlı taramada bu kalem bir önceki döneme göre 1.141 sayfa azalmıştır.</t>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/cheers-to-nails-3-lu-oje-seti-set142/</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Cheers to Nails 3'lü Oje Seti</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Cheers to Nails 3'lü Oje Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/flormar-kurumsal-hediye/</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Kurumsal Hediyeler</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Hediye Kutusu Çeşitleri</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/yuksek-pigmentli-yari-mat-bitisli-ince-yapili-kompakt-pudra-kahverengi-8682536051385/</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Yüksek Pigmentli &amp; Yarı Mat Bitişli İnce Yapılı Kompakt Pudra</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Compact Powder</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/baked-blush-on-yuksek-pigmentli-dogal-isiltili-firinlanmis-allik-seftali-8682536080224/</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Baked Blush-On Yüksek Pigmentli &amp; Doğal Işıltılı Fırınlanmış Allık</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Baked Blush-On Yüksek Pigmentli &amp; Doğal Işıltılı Fırınlanmış Allık</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/dewy-lip-glaze-parlak-dolgun-gorunum-veren-yapismayan-dudak-parlaticisi-kiremit-8682536068055/</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Dewy Lip Glaze Parlak &amp; Dolgun Görünüm Veren Yapışmayan Dudak Parlatıcısı</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Dewy Lip Glaze Nemlendirici Etkili Yarı Transparan Dudak Parlatıcısı 003</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/kiss-me-more-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-pembe-8682536040662/</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Kiss Me More Yüksek Pigmentli &amp; Mat Bitişli Nemlendirici Likit Ruj</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Kiss Me More Yüksek Pigmentli &amp; Mat Bitişli Nemlendirici Likit Ruj 005</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/juicy-lips-3-lu-dudak-seti-renkli-set207/</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Juicy Lips 3'lu Dudak Seti</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Juicy Lips 3'lü Dudak Seti içerisindeki ürünler:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/treasure-lashes-2-li-goz-makyaji-seti-renkli-set209/</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Treasure Lashes 2'li Göz Makyajı Seti</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Treasure Lashes 2'li Göz Makyajı Seti içerisin...</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/blush-on-yuksek-pigmentli-mat-bitisli-kompakt-toz-allik-pembe-8682536083140/</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Blush-On Yüksek Pigmentli &amp; Mat Bitişli Kompakt Toz Allık</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Blush-On Yüksek Pigmentli &amp; Yoğun Işıltılı Kompakt Toz Allık</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/strawberry-makeup-4-lu-makyaj-seti-renkli-set086/</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Strawberry Makeup 4'lü Makyaj Seti</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Strawberry Makeup 4'lü M...</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/bridal-6-li-oje-seti-renkli-set078/</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Bridal 6'lı Oje Seti</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Bridal 6'lı Oje Seti İçerisindeki Ürünler</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/baked-yuksek-pigmentli-mat-bitisli-firinlanmis-goz-fari-bej-8682536052429/</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Baked Yüksek Pigmentli &amp; Mat Bitişli Fırınlanmış Göz Farı</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Baked Yüksek Pigmentli &amp; Mat Bitişli Fırınlanmış Göz Farı</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/dewy-lip-glaze-parlak-dolgun-gorunum-veren-yapismayan-dudak-parlaticisi-lila-8682536069465/</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Dewy Lip Glaze Parlak &amp; Dolgun Görünüm Veren Yapışmayan Dudak Parlatıcısı</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Dewy Lip Glaze Nemlendirici Etkili Yarı Transparan Dudak Parlatıcısı</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/camouflage-palette-renk-dengeleyici-4-lu-krem-kapatici-paleti-karisik-8682536085892/</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Camouflage Palette Renk Dengeleyici 4'lü Krem Kapatıcı Paleti</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Camouflage Palette Renk Dengeleyici 4'lü Krem Kapatıcı Paleti 000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/dewy-lip-glaze-parlak-dolgun-gorunum-veren-yapismayan-dudak-parlaticisi-mercan-8682536069441/</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Dewy Lip Glaze Parlak &amp; Dolgun Görünüm Veren Yapışmayan Dudak Parlatıcısı</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Dewy Lip Glaze Nemlendirici Etkili Yarı Transparan Dudak Parlatıcısı</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-yari-transparan-mat-bitisli-nemlendirici-dudak-pudrasi-pembe-8682536094290/</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Lightweight Yarı Transparan &amp; Mat Bitişli Nemlendirici Dudak Pudrası</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Lightweight Yarı Transparan&amp;Mat Bitişli Nemlendirici Dudak Pudrası</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-pembe-8682536108799/</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Mono Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/pretty-in-pink-kit-makyaj-seti-pembe-set064/</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Pretty in Pink Kit Makyaj Seti</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Set içerisindeki ürünler:</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/meyve-ozleriyle-renkli-dudaklar-2-li-lip-balm-tint-seti-pembe-set139/</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Meyve Özleriyle Renkli Dudaklar 2'li Lip Balm&amp;Tint Seti</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Meyve Özleriyle Renkli Dudaklar 2'li Lip Balm &amp; Tint Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-yari-transparan-mat-bitisli-nemlendirici-dudak-pudrasi-pembe-8682536048897/</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Lightweight Yarı Transparan &amp; Mat Bitişli Nemlendirici Dudak Pudrası</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Lightweight Yarı Transparan&amp;Mat Bitişli Nemlendirici Dudak Pudrası</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/hafif-yaz-makyaji-3-lu-makyaj-seti-renkli-set188/</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Hafif Yaz Makyajı 3'lü Makyaj Seti</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Hafif Yaz Makyajı 3'lü Makyaj Seti içerisinde:...</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/beklemeyi-sevmeyenlere-hizli-kuruyan-5-li-oje-seti-renkli-set140/</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Beklemeyi Sevmeyenlere Hızlı Kuruyan 5'li Oje Seti</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Beklemeyi Sevmeyenlere Hızlı Kuruyan 5'li Oje Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/the-lip-ritual-3-lu-dudak-makyaji-seti-renkli-set212/</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>The Lip Ritual 3'lü Dudak Makyajı Seti</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>The Lip Ritual 3'lü Dudak Makyajı Seti içeris...</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-bronz-8682536108614/</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Mono Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/baked-blush-on-yuksek-pigmentli-dogal-isiltili-firinlanmis-allik-pembe-8682536051491/</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Baked Blush-On Yüksek Pigmentli &amp; Doğal Işıltılı Fırınlanmış Allık</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Baked Blush-On Yüksek Pigmentli &amp; Doğal Işıltılı Fırınlanmış Allık</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/duo-delight-makyaj-seti-renkli-set068/</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Duo Delight Makyaj Seti</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Set içerisindeki ürünler:</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/pratik-4-lu-makyaj-seti-renkli-set191/</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Pratik 4'lü Makyaj Seti</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Pratik 4'lü Makyaj Seti içerisinde:</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/cerezlere-iliskin-aydinlatma-metni/</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Çerezlere İlişkin Aydınlatma Metni</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>ÇEREZLERE İLİŞKİN AYDINLATMA METNİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-kahverengi-8682536108737/</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Mono Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mat-smooth-2-li-dudak-seti-renkli-set208/</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Mat &amp; Smooth 2'li Dudak Seti</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Mat &amp; Smooth 2'li Dudak Seti içerisindeki ürünler:</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/wet-dry-mat-bitisli-kremsi-kompakt-pudra-bej-8682536053679/</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Wet &amp; Dry Mat Bitişli Kremsi Kompakt Pudra</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Wet &amp; Dry Mat Bitişli Kremsi Kompakt Pudra</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/baked-blush-on-yuksek-pigmentli-dogal-isiltili-firinlanmis-allik-seftali-8682536051439/</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Baked Blush-On Yüksek Pigmentli &amp; Doğal Işıltılı Fırınlanmış Allık</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Baked Blush-On Yüksek Pigmentli &amp; Doğal Işıltılı Fırınlanmış Allık</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/kiss-me-more-yuksek-pigmentli-mat-bitisli-nemlendirici-likit-ruj-pembe-8682536040921/</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Kiss Me More Yüksek Pigmentli &amp; Mat Bitişli Nemlendirici Likit Ruj</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Kiss Me More Yüksek Pigmentli &amp; Mat Bitişli Nemlendirici Likit Ruj 025</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/yuksek-pigmentli-yari-mat-bitisli-ince-yapili-kompakt-pudra-pembe-8682536051309/</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Yüksek Pigmentli &amp; Yarı Mat Bitişli İnce Yapılı Kompakt Pudra</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Compact Powder</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/suya-dayanikli-3-lu-goz-makyaji-seti-renkli-set048/</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Suya Dayanıklı 3'lü Göz Makyajı Seti</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Set İçe...</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lift-up-dolgun-gorunum-veren-2-li-kirmizi-dudak-seti-kirmizi-set195/</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Lift Up Dolgun Görünüm Veren 2'li Kırmızı Dudak Seti</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Lift Up Kırmızı 2'li Dudak Kombosu içerisinde:...</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/baked-yuksek-pigmentli-mat-bitisli-firinlanmis-goz-fari-bej-8682536052344/</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Baked Yüksek Pigmentli &amp; Mat Bitişli Fırınlanmış Göz Farı</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Baked Yüksek Pigmentli &amp; Mat Bitişli Fırınlanmış Göz Farı</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/summer-jam-4-lu-makyaj-seti-renkli-set079/</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Summer Jam 4'lü Makyaj Seti</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Summer Jam 4'lü Makyaj Seti içerisindeki ürünler:</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/wet-dry-mat-bitisli-kremsi-kompakt-pudra-pembe-8682536053716/</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Wet &amp; Dry Mat Bitişli Kremsi Kompakt Pudra</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Wet &amp; Dry Mat Bitişli Kremsi Kompakt Pudra</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lift-up-dolgun-gorunum-veren-2-li-nude-dudak-seti-kahverengi-set196/</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Lift Up Dolgun Görünüm Veren 2'li Nude Dudak Seti</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Lift Up Doğal Görünümlü 2'li Dudak Kombos...</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/wet-dry-mat-bitisli-kremsi-kompakt-pudra-kahverengi-8682536053778/</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Wet &amp; Dry Mat Bitişli Kremsi Kompakt Pudra</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Wet &amp; Dry Mat Bitişli Kremsi Kompakt Pudra</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/color-palette-ince-yapili-mat-bitisli-isiltili-4-lu-goz-fari-paleti-bej-kahverengi-8682536121217/</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Color Palette İnce Yapılı &amp; Mat Bitişli/Işıltılı 4'lü Göz Farı Paleti</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Color Palette İnce Yapılı &amp; Doğal Işıltılı 4'lü Kompakt Göz Farı Paleti</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/blush-on-yuksek-pigmentli-yogun-isiltili-kompakt-toz-allik-pembe-8682536051736/</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Blush-On Yüksek Pigmentli &amp; Yoğun Işıltılı Kompakt Toz Allık</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Blush-On Yüksek Pigmentli &amp; Yoğun Işıltılı Kompakt Toz Allık Y103</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/kadife-dokulu-ince-yapili-firinlanmis-aydinlatici-pudra-bronz-8682536053372/</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Kadife Dokulu &amp; İnce Yapılı Fırınlanmış Aydınlatıcı Pudra</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Kadife Dokulu &amp; İnce Yapılı Fırınlanmış Aydınlatıcı Pudra 003</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-siyah-8682536108935/</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Mono Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/wet-dry-mat-bitisli-kremsi-kompakt-pudra-kahverengi-8682536090711/</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Wet &amp; Dry Mat Bitişli Kremsi Kompakt Pudra</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Wet &amp; Dry Mat Bitişli Kremsi Kompakt Pudra</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/baked-blush-on-yuksek-pigmentli-dogal-isiltili-firinlanmis-allik-pembe-8682536080248/</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Baked Blush-On Yüksek Pigmentli &amp; Doğal Işıltılı Fırınlanmış Allık</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Baked Blush-On Yüksek Pigmentli &amp; Doğal Işıltılı Fırınlanmış Allık</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/color-palette-ince-yapili-mat-bitisli-isiltili-4-lu-goz-fari-paleti-beyaz-pembe-8682536107730/</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Color Palette İnce Yapılı &amp; Mat Bitişli/Işıltılı 4'lü Göz Farı Paleti</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Color Palette İnce Yapılı &amp; Doğal Işıltılı 4'lü Kompakt Göz Farı Paleti</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/love-basics-4lu-makyaj-seti-set274/</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Love Basics 4’lü Makyaj Seti</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Love Basics 4’lü Makyaj Seti İçerisindeki Ürünler:</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/hydra-radiance-2-li-yuz-makyaji-seti-renkli-set210/</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Hydra Radiance 2'li Yüz Makyajı Seti</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Hydra Radiance 2'li Yüz Makyajı Seti içerisinde...</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/signature-selection-makyaj-seti-renkli-set069/</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Signature Selection Makyaj Seti</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Set içerisindeki ürünler:</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-bej-8682536108478/</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Mono Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/baked-yuksek-pigmentli-yogun-isiltili-firinlanmis-goz-fari-altin-8682536052443/</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Baked Yüksek Pigmentli &amp; Yoğun Işıltılı Fırınlanmış Göz Farı</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Baked Yüksek Pigmentli &amp; Yoğun Işıltılı Fırınlanmış Göz Farı</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/lightweight-yari-transparan-mat-bitisli-nemlendirici-dudak-pudrasi-seftali-8682536094337/</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Lightweight Yarı Transparan &amp; Mat Bitişli Nemlendirici Dudak Pudrası</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Lightweight Yarı Transparan&amp;Mat Bitişli Nemlendirici Dudak Pudrası</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/color-palette-ince-yapili-mat-bitisli-isiltili-4-lu-goz-fari-paleti-beyaz-gri-siyah-8682536121194/</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Color Palette İnce Yapılı &amp; Mat Bitişli/Işıltılı 4'lü Göz Farı Paleti</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Color Palette İnce Yapılı &amp; Doğal Işıltılı 4'lü Kompakt Göz Farı Paleti</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/basak-burcu-3-lu-makyaj-seti-renkli-set107/</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Başak Burcu 3'lü Makyaj Seti</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Başak Burcu 3'lü Makyaj Seti</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/mono-yuksek-pigmentli-dogal-isiltili-kompakt-goz-fari-bakir-8682536108751/</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Mono Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Flormar Yüksek Pigmentli &amp; Doğal Işıltılı Kompakt Göz Farı</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>NOT: A sütunundaki sayfada birden fazla H1 etiketi bulunmaktadır; ikinci başlık H2 seviyesine indirilmelidir. Kayıtların 80'i ürün sayfasıdır ve ikinci H1 çoğunlukla aynı ürün adının marka önekli varyantıdır; düzeltme ürün şablonu düzeyinde yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -4767,7 +11578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -4801,7 +11612,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/far-paleti-ve-goz-fari/</t>
+          <t>https://flormar.com.tr/sedefli-oje/</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -4809,59 +11620,59 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/goz-fari/</t>
+          <t>https://www.flormar.com.tr/sedefli-oje/</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Kategori birleştirme</t>
+          <t>www yönlendirmesi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/indirimli-urun-kampanyasi/</t>
+          <t>https://www.flormar.com.tr/account/profile-extra/</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/</t>
+          <t>https://www.flormar.com.tr/users/auth/?next=/account/profile-extra/</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Kampanya kapanışı</t>
+          <t>Oturum yönlendirmesi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/kampanyalar</t>
+          <t>https://www.flormar.com.tr/account/student-verification/</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/kampanyalar/</t>
+          <t>https://www.flormar.com.tr/users/auth/?next=/account/student-verification/</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Sonda eğik çizgi</t>
+          <t>Oturum yönlendirmesi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>https://flormar.com.tr/sedefli-oje/</t>
+          <t>https://www.flormar.com.tr/latte-nail-enamel-yuksek-pigmentli-parlak-bitisli-oje-pembe-ten-rengi-8682536104517/</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -4869,19 +11680,19 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/sedefli-oje/</t>
+          <t>https://www.flormar.com.tr/latte-yuksek-pigmentli-parlak-bitisli-kahve-tonlu-oje-pembe-ten-rengi-8682536104517/</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>www yönlendirmesi</t>
+          <t>Slug güncellemesi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/ergonomik-yumusak-silikonlu-kirpik-kivirici-8690604598359/</t>
+          <t>https://www.flormar.com.tr/kadin-parfum/</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -4889,119 +11700,359 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/ergonomik-yumusak-silikonlu-kirpik-kivirici-gumus-8690604598359/</t>
+          <t>https://www.flormar.com.tr/parfum/</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Slug güncellemesi</t>
+          <t>Kategori birleştirme</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/glow-lip-oil-nemlendirici-etkili-isiltili-bitisli-renkli-dudak-yagi-8682536104074/</t>
+          <t>https://www.flormar.com.tr/account/favourite-products/</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/glow-lip-oil-nemlendirici-etkili-isiltili-bitisli-renkli-dudak-yagi-pembe-8682536104074/</t>
+          <t>https://www.flormar.com.tr/users/auth/?next=/account/favourite-products/</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Slug güncellemesi</t>
+          <t>Oturum yönlendirmesi</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/account/profile-extra/</t>
+          <t>https://www.flormar.com.tr/indirimli-urun-kampanyasi/</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/users/auth/?next=/account/profile-extra/</t>
+          <t>https://www.flormar.com.tr/</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Oturum yönlendirmesi</t>
+          <t>Kampanya kapanışı</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/users/orders/</t>
+          <t>http://flormar.com.tr/</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/users/auth/?next=/users/orders/</t>
+          <t>https://www.flormar.com.tr/</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Oturum yönlendirmesi</t>
+          <t>Kampanya kapanışı</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/account/favourite-products/</t>
+          <t>https://www.flormar.com.tr/kampanyalar</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/users/auth/?next=/account/favourite-products/</t>
+          <t>https://www.flormar.com.tr/kampanyalar/</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Oturum yönlendirmesi</t>
+          <t>Sonda eğik çizgi</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>https://www.flormar.com.tr/account/student-verification/</t>
+          <t>https://www.flormar.com.tr/far-paleti-ve-goz-fari/</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/goz-fari/</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Kategori birleştirme</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/users/orders/</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
         <v>302</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>https://www.flormar.com.tr/users/auth/?next=/account/student-verification/</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/users/auth/?next=/users/orders/</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Oturum yönlendirmesi</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>NOT: A sütunundaki URL'ye site içinden verilen bağlantılar C sütunundaki nihai adresle güncellenmelidir. 302 kayıtları oturum gerektiren hesap sayfalarına aittir ve beklenen davranıştır. 301 kayıtlarında zincir veya döngü tespit edilmemiştir.</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/ergonomik-yumusak-silikonlu-kirpik-kivirici-8690604598359/</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/ergonomik-yumusak-silikonlu-kirpik-kivirici-gumus-8690604598359/</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Slug güncellemesi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/golden-glam-shimmer-oil-monoi-tahiti-ozlu-isiltili-sac-ve-vucut-yagi-transparan-8682536114066/</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/golden-glam-shimmer-oil-nemlendirici-etkili-bronz-isiltili-sac-ve-vucut-yagi-transparan-8682536114066/</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Slug güncellemesi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/kvkk</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/kvkk/</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Sonda eğik çizgi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/users/auth/www.flormar.com.tr</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Kampanya kapanışı</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/cerezlere-iliskin-aydinlatma-metni</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/cerezlere-iliskin-aydinlatma-metni/</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Sonda eğik çizgi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/cerez-politikasi/</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/cerezlere-iliskin-aydinlatma-metni/</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Kategori birleştirme</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/metaglam-yuksek-pigmentli-yogun-parlak-bitisli-isiltili-metalik-oje-pembe-8682536080507/</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/metaglam-yuksek-pigmentli-yogun-parlak-bitisli-isiltili-metalik-oje-beyaz-8682536080507/</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Slug güncellemesi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/nemlendiricili-fondoten/</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/fondoten/</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Kategori birleştirme</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/glow-lip-oil-nemlendirici-etkili-isiltili-bitisli-renkli-dudak-yagi-8682536104074/</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/glow-lip-oil-nemlendirici-etkili-isiltili-bitisli-renkli-dudak-yagi-pembe-8682536104074/</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Slug güncellemesi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>http://www.flormar.com.tr/</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Kampanya kapanışı</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/account/profile-extra-campaigns/</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>302</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flormar.com.tr/users/auth/?next=/account/profile-extra-campaigns/</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Oturum yönlendirmesi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>NOT: A sütunundaki URL'ye site içinden verilen bağlantılar C sütunundaki nihai adresle güncellenmelidir. 302 kayıtları oturum gerektiren hesap sayfalarına aittir ve beklenen davranıştır. 301 kayıtlarında zincir veya döngü tespit edilmemiştir. Liste, 12 Ağu site geneli taramasındaki site içi yönlendirmelerin tamamıdır; eski kategori adresine dönen kayıt bulunmamaktadır.</t>
         </is>
       </c>
     </row>
